--- a/AAII_Financials/Quarterly/MS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="92">
   <si>
     <t>MS</t>
   </si>
@@ -656,516 +656,528 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="25" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="42" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="26" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>21250000</v>
+      </c>
+      <c r="E8" s="3">
         <v>20482000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17872000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>18224000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>16596000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>17604000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>16108000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>15304000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>14943000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>15142000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>12893000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>13139000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>13296000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14283000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>19662000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>16577000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14462000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>15235000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>14846000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>15041000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>15106000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>16128000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>13971000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>12291000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>14418000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>11926000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>13376000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>13164000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>13721000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>13562000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>11670000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>12563000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>12998000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>12962000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>11091000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>10754000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>10858000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>10939000</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>10006000</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>9640000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2667000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2404000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2288000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2260000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2277000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2272000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2239000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2086000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2006000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1897000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1852000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1802000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1801000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1796000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>7764000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>4438000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2208000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1316000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1133000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1113000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1142000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1319000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1150000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1267000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1474000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2887000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>3152000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>3769000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>4107000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3869000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3720000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>3250000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2997000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2512000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2675000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2613000</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2441000</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>2230000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>2043000</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1711000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>18583000</v>
+      </c>
+      <c r="E10" s="3">
         <v>18078000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>15584000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>15964000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>14319000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>15332000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>13869000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>13218000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>12937000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>13245000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>11041000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>11337000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>11495000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>12487000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>11898000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>12139000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>12254000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>13919000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>13713000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>13928000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>13964000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>14809000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>12821000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>11024000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>12944000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>9039000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>10224000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>9395000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>9614000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>9693000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>7950000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>9313000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>10001000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>10450000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>8416000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>8141000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>8417000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>8709000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>7963000</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>7929000</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1330,8 +1343,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1452,50 +1468,53 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E14" s="3">
         <v>179000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>28000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>41000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>5000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>38000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>10000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>321000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1505,8 +1524,8 @@
       <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1574,53 +1593,56 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1202000</v>
+      </c>
+      <c r="E15" s="3">
         <v>714000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1138000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1348000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1307000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>865000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>1645000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1270000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1271000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>975000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>1406000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>988000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>922000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>940000</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1696,8 +1718,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,252 +1762,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>12417000</v>
+      </c>
+      <c r="E17" s="3">
         <v>12163000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>10969000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>11140000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>10934000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11154000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10132000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>10227000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>9928000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>9890000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>9332000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>9143000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>9537000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>9603000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>16868000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>13189000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>11143000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>10647000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>9962000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>10167000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>10540000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>10784000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>9541000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>8804000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>10063000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>9780000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>10643000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>10454000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>10818000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>10607000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>9813000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>9712000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>9889000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>9542000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>8620000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>8272000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>8216000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>8131000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>7760000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>7259000</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>8833000</v>
+      </c>
+      <c r="E18" s="3">
         <v>8319000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>6903000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>7084000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5662000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>6450000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5976000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5077000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5015000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5252000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3561000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3996000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>3759000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>4680000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2794000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>3388000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>3319000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>4588000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>4884000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>4874000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4566000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5344000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4430000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>3487000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4355000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>2146000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>2733000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>2710000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>2903000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>2955000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>1857000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>2851000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>3109000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>3420000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>2471000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>2482000</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>2642000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>2808000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>2246000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>2381000</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2025,53 +2057,54 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1480000</v>
+      </c>
+      <c r="E20" s="3">
         <v>1129000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1115000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1048000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>999000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>901000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1032000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>846000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>939000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>857000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1144000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>849000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>936000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>920000</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -2147,130 +2180,136 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>8555000</v>
+      </c>
+      <c r="E21" s="3">
         <v>7904000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>6926000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>7384000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>5970000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>6414000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>6589000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>5501000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>5347000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>5370000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3823000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>4135000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>3745000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4700000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4001000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>4316000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>4240000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>5530000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>6121000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>5909000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>5623000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>6231000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>5836000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>4340000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>5041000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>2970000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>3389000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>3364000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>3578000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>3613000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>2326000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>3319000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>3626000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>3810000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>2884000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>2933000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>3097000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>3242000</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>2625000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>2859000</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2313,8 +2352,8 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2391,252 +2430,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>7348000</v>
+      </c>
+      <c r="E23" s="3">
         <v>7011000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>5760000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>6028000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4622000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>5544000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4906000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4221000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4074000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>4395000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2096000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3145000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2812000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>3760000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2794000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>3388000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>3319000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>4588000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>4884000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>4874000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>4566000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5344000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>4430000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>3487000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>4355000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>2146000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>2733000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>2710000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>2903000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>2955000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>1857000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>2851000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3109000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3420000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>2471000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>2482000</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2642000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>2808000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>2246000</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>2381000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1695000</v>
+      </c>
+      <c r="E24" s="3">
         <v>1373000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>1336000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1373000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1047000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>1173000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1182000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>995000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>957000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>933000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>555000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>710000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>591000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>727000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>528000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>726000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>783000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>873000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1168000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1150000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1054000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1176000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1018000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>736000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1119000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>366000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>428000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>492000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>657000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>487000</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>300000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>696000</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>640000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>714000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>843000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>697000</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>846000</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>815000</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>566000</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>749000</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2757,252 +2805,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5653000</v>
+      </c>
+      <c r="E26" s="3">
         <v>5638000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4424000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>4655000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3575000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>4371000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3724000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3226000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3117000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3462000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1541000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2435000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2221000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3033000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>2266000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>2662000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>2536000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>3715000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>3716000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3724000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3512000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4168000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3412000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>2751000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3236000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>1780000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>2305000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>2218000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>2246000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>2468000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>1557000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>2155000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>2469000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>2706000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>1628000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>1785000</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1796000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>1993000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>1680000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>1632000</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>5436000</v>
+      </c>
+      <c r="E27" s="3">
         <v>5411000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>4250000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>4450000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3392000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>4157000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3564000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3028000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2942000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>3266000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1383000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2262000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2049000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2836000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2113000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>2494000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>2391000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>3542000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>3592000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3584000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3408000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3982000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3266000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>2597000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3047000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>1590000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>2085000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>2060000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>2031000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>2336000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>1360000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>2020000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>2269000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>2577000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>1438000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>1682000</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1592000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>1862000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>1509000</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>1510000</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3123,8 +3180,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3197,14 +3257,14 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD29" s="3">
         <v>0</v>
@@ -3216,37 +3276,40 @@
         <v>0</v>
       </c>
       <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH29" s="3">
         <v>1000</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-1000</v>
-      </c>
-      <c r="AI29" s="3">
-        <v>-2000</v>
       </c>
       <c r="AJ29" s="3">
         <v>-2000</v>
       </c>
       <c r="AK29" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-965000</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>6000</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>-5000</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>-22000</v>
       </c>
-      <c r="AO29" s="3">
-        <v>0</v>
-      </c>
       <c r="AP29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AQ29" s="3">
         <v>8000</v>
       </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3367,8 +3430,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3489,53 +3555,56 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1480000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1129000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1115000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1048000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-999000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-901000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1032000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-846000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-939000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-857000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1144000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-849000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-936000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-920000</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3611,130 +3680,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>5581000</v>
+      </c>
+      <c r="E33" s="3">
         <v>5567000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4397000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>4610000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3539000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>4315000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3714000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3188000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3076000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>3412000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1517000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2408000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2182000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2980000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2113000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>2494000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>2391000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>3542000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>3592000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3584000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3408000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3982000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3266000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>2597000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3047000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>1590000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>2085000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>2060000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>2031000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>2336000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>1361000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>2019000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>2267000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>2575000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>473000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>1688000</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1587000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1840000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>1509000</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3855,257 +3930,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>5581000</v>
+      </c>
+      <c r="E35" s="3">
         <v>5567000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4397000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>4610000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3539000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>4315000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3714000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3188000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3076000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>3412000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1517000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2408000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2182000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2980000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2113000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>2494000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>2391000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>3542000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>3592000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3584000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3408000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3982000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3266000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>2597000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3047000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>1590000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>2085000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>2060000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>2031000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>2336000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>1361000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>2019000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>2267000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>2575000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>473000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>1688000</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1587000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1840000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>1509000</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4148,8 +4232,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4192,175 +4277,179 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>160135000</v>
+      </c>
+      <c r="E41" s="3">
         <v>133529000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>111695000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>103734000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>109130000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>90739000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>105386000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>91084000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>90160000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>102305000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>89232000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>108401000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104994000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>111258000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>128127000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>111696000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>131286000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>136086000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>127725000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>123863000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>126480000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>118118000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>105654000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>94772000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>106276000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>131509000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>49659000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>48917000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>49145000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>49970000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>51840000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>59279000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>30176000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>29073000</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>24816000</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>24047000</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>25008000</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>22081000</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>22017000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>26899000</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>578941000</v>
+      </c>
+      <c r="E42" s="3">
         <v>529776000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>488696000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>467043000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>453872000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>458216000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>427277000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>483543000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>438503000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>624742000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>437269000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>432728000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>443281000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>461985000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
         <v>0</v>
       </c>
@@ -4436,130 +4525,136 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>438136000</v>
+      </c>
+      <c r="E43" s="3">
         <v>405425000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>381902000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>367322000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>342555000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>323122000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>310078000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>307209000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>300044000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>283909000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>282428000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>278175000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>275000000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>272857000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>78540000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>87935000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>82759000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>94804000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>96018000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>98353000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>100921000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>115043000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>97737000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>72537000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>62290000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>74424000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>55646000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>59514000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>53381000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>52667000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>53298000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>60839000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>61714000</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>66835000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>56187000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>54388000</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>54917000</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>48344000</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>46460000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>51411000</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4602,8 +4697,8 @@
       <c r="P44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
+      <c r="Q44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R44" s="3">
         <v>0</v>
@@ -4680,53 +4775,56 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>278278000</v>
+      </c>
+      <c r="E45" s="3">
         <v>283742000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>213269000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>199429000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>219770000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>203124000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>148945000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>150702000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>161797000</v>
       </c>
-      <c r="L45" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>162698000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>137504000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>123705000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>127205000</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
-      </c>
       <c r="R45" s="3">
         <v>0</v>
       </c>
@@ -4802,53 +4900,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1468547000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1369703000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1204936000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1148961000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1137659000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1091312000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1004005000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1045400000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1005787000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1024382000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>986882000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>971038000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>962264000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>988451000</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4924,166 +5025,172 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>155332000</v>
+      </c>
+      <c r="E47" s="3">
         <v>162538000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>165610000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>165574000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>165663000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>160266000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>161548000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>162886000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>157374000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>154544000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>156722000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>148741000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>153662000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>159906000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>924239000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>912876000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>912019000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>944834000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>917927000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>919892000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>887445000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>880621000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>876524000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>762334000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>780684000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>715283000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>730608000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>736894000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>732314000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>716811000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>661804000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>659127000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>696319000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>671395000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>682636000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>687138000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>676418000</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>674093000</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>656680000</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>647210000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E48" s="3">
+      <c r="E48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="3">
         <v>4164000</v>
       </c>
-      <c r="F48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I48" s="3">
+      <c r="I48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J48" s="3">
         <v>4114000</v>
       </c>
-      <c r="J48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="K48" s="3" t="s">
         <v>8</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M48" s="3">
+      <c r="M48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N48" s="3">
         <v>4368000</v>
       </c>
-      <c r="N48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5102,12 +5209,12 @@
       <c r="T48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U48" s="3">
+      <c r="U48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V48" s="3">
         <v>4268000</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5126,21 +5233,21 @@
       <c r="AB48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AC48" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD48" s="3">
         <v>3998000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3825000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3859000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3886000</v>
       </c>
-      <c r="AG48" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH48" s="3" t="s">
         <v>8</v>
       </c>
@@ -5150,8 +5257,8 @@
       <c r="AJ48" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK48" s="3">
-        <v>0</v>
+      <c r="AK48" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL48" s="3">
         <v>0</v>
@@ -5168,130 +5275,136 @@
       <c r="AP48" s="3">
         <v>0</v>
       </c>
+      <c r="AQ48" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>22978000</v>
+      </c>
+      <c r="E49" s="3">
         <v>23065000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>22736000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>22822000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>22919000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>23019000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>23159000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>23355000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>23482000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>23636000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>23762000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>23903000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>23974000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>24127000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>24270000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>24614000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>24803000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>25069000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>25193000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>25346000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>25528000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>25682000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>16615000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>9228000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>9287000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>9146000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>9250000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>9350000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>9434000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>8770000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>8851000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>8920000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>9024000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>9133000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>9045000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>9081000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>9158000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>9232000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>9298000</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>9331000</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5412,8 +5525,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5534,53 +5650,56 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>28200000</v>
+      </c>
+      <c r="E52" s="3">
         <v>26112000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>22824000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>27449000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>27629000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>25699000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22245000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>26386000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25804000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25941000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>21959000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25331000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>25011000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>27420000</v>
       </c>
-      <c r="Q52" s="3">
-        <v>0</v>
-      </c>
       <c r="R52" s="3">
         <v>0</v>
       </c>
@@ -5611,39 +5730,39 @@
       <c r="AA52" s="3">
         <v>0</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC52" s="3">
+      <c r="AB52" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD52" s="3">
         <v>32512000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>30739000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>30435000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>30712000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>35356000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>33202000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>32706000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>35291000</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>34231000</v>
       </c>
-      <c r="AL52" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM52" s="3" t="s">
         <v>8</v>
       </c>
@@ -5656,8 +5775,11 @@
       <c r="AP52" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ52" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5778,130 +5900,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>1675057000</v>
+      </c>
+      <c r="E54" s="3">
         <v>1581418000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>1420270000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>1364806000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1353870000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1300296000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1215071000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>1258027000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>1212447000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>1228503000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>1193693000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>1169013000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>1164911000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1199904000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1180231000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>1160029000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>1173776000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>1222233000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>1188140000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>1190476000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>1161805000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>1158772000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>1115862000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>955940000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>975363000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>947795000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>895429000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>902604000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>891959000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>875964000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>853531000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>865517000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>875875000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>858495000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>851733000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>853693000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>841016000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>832391000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>814949000</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>813891000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5944,8 +6072,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5988,345 +6117,352 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>273801000</v>
+      </c>
+      <c r="E57" s="3">
         <v>254670000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>221856000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>222050000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>211185000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>197941000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>172000000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>211118000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>200560000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>214370000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>203788000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>195761000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>212647000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>216743000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>211861000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>226062000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>231107000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>240950000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>226521000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>237945000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>231293000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>227792000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>225318000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>189755000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>196413000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>198074000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>197834000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>202915000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>192098000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>193092000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>179559000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>191026000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>201737000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>194924000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>191510000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>198792000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>197055000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>189544000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>190513000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>194007000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>230880000</v>
+      </c>
+      <c r="E58" s="3">
         <v>227376000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>188604000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>140692000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>163499000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>161922000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>150007000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>134971000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>138594000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>157694000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>148077000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>133023000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>112184000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>121597000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>439050000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>415415000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>431310000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>439276000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>427825000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>406986000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>393115000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>410751000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>372791000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>294575000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>308201000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>305853000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>276031000</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>249891000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>249212000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>240187000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>249487000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>235513000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>223452000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>211999000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>215860000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>209709000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>196526000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>209756000</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>211432000</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>199693000</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>224512000</v>
+      </c>
+      <c r="E59" s="3">
         <v>211711000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>171924000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>139982000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>153955000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>162869000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>115834000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>130317000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>141584000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>148641000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>116238000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>135921000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>134514000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>164382000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4273000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3401000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>2900000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>2659000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7321000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>2374000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>2517000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>2329000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>2119000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>2545000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>2558000</v>
       </c>
-      <c r="AB59" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC59" s="3">
+      <c r="AC59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD59" s="3">
         <v>4778000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4535000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4595000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4653000</v>
       </c>
-      <c r="AG59" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AH59" s="3" t="s">
         <v>8</v>
       </c>
@@ -6336,8 +6472,8 @@
       <c r="AJ59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK59" s="3">
-        <v>0</v>
+      <c r="AK59" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AL59" s="3">
         <v>0</v>
@@ -6354,53 +6490,56 @@
       <c r="AP59" s="3">
         <v>0</v>
       </c>
+      <c r="AQ59" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>734462000</v>
+      </c>
+      <c r="E60" s="3">
         <v>698376000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>587047000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>507119000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>532799000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>526522000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>441779000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>481879000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>486075000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>520705000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>472463000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>469423000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>463518000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>506679000</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6476,175 +6615,181 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>376616000</v>
+      </c>
+      <c r="E61" s="3">
         <v>352136000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>324804000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>326336000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>315695000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>287414000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>268574000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>289755000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>268861000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>259139000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>246710000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>246174000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>244578000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>242363000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>233867000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>216361000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>221979000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>225671000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>227363000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>224937000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>218604000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>191263000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>213388000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>197422000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>195453000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>181689000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>169658000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>193659000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>197848000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>190691000</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>189662000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>190889000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>192244000</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>194964000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>192582000</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>191677000</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>184112000</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>172688000</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>164775000</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>163927000</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>446539000</v>
+      </c>
+      <c r="E62" s="3">
         <v>415522000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>395767000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>420300000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>396106000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>378513000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>399290000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>381722000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>355905000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>348519000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>374538000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>353258000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>355454000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>348908000</v>
       </c>
-      <c r="Q62" s="3">
-        <v>0</v>
-      </c>
       <c r="R62" s="3">
         <v>0</v>
       </c>
@@ -6720,8 +6865,11 @@
       <c r="AP62" s="3">
         <v>0</v>
       </c>
+      <c r="AQ62" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6842,8 +6990,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6964,8 +7115,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7086,130 +7240,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1557617000</v>
+      </c>
+      <c r="E66" s="3">
         <v>1466034000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1307618000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1253755000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1244600000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1192449000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1109643000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>1153356000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>1110841000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>1128363000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>1093711000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>1068855000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>1063550000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1097950000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1080090000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1059018000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1072180000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1119332000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1082699000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1084573000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>1054935000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1052513000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1014081000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>867546000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>888718000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>861935000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>813880000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>820222000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>810235000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>795240000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>773285000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>786814000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>796766000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>780461000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>774342000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>774715000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>762190000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>754467000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>738899000</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>736742000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7252,8 +7412,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7374,8 +7535,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7496,8 +7660,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7523,7 +7690,7 @@
         <v>9750000</v>
       </c>
       <c r="K70" s="3">
-        <v>8750000</v>
+        <v>9750000</v>
       </c>
       <c r="L70" s="3">
         <v>8750000</v>
@@ -7547,7 +7714,7 @@
         <v>8750000</v>
       </c>
       <c r="S70" s="3">
-        <v>7750000</v>
+        <v>8750000</v>
       </c>
       <c r="T70" s="3">
         <v>7750000</v>
@@ -7565,10 +7732,10 @@
         <v>7750000</v>
       </c>
       <c r="Y70" s="3">
+        <v>7750000</v>
+      </c>
+      <c r="Z70" s="3">
         <v>9250000</v>
-      </c>
-      <c r="Z70" s="3">
-        <v>8520000</v>
       </c>
       <c r="AA70" s="3">
         <v>8520000</v>
@@ -7613,13 +7780,16 @@
         <v>8520000</v>
       </c>
       <c r="AO70" s="3">
-        <v>7520000</v>
+        <v>8520000</v>
       </c>
       <c r="AP70" s="3">
         <v>7520000</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>7520000</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7740,130 +7910,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>122774000</v>
+      </c>
+      <c r="E72" s="3">
         <v>118913000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>115091000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>112426000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>109567000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>107653000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>104989000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>102911000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>101374000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>99811000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>97996000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>98007000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>97151000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>96392000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>94862000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>94055000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>92889000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>91722000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>89432000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>87099000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>84791000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>82034000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>78694000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>76061000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>74015000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>71518000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>70589000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>69071000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>67588000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>66061000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>64175000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>63330000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>61835000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>60009000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>57577000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>57554000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>56325000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>55109000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>53679000</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>52545000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7984,8 +8160,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8106,8 +8285,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8228,130 +8410,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>106579000</v>
+      </c>
+      <c r="E76" s="3">
         <v>104536000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>101882000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>100212000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>98434000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>97062000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>94761000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>93897000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>91964000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>90448000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>90288000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>90461000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>91636000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>92076000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>91391000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>92261000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>93846000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>95151000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>97691000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>98153000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>99120000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>98509000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>92531000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>79874000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>78125000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>77340000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>73029000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>73862000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>73204000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>72204000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>71726000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>70183000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>70589000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>69514000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>68871000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>70458000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>70306000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>69404000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>68530000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>69629000</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8472,257 +8660,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>5581000</v>
+      </c>
+      <c r="E81" s="3">
         <v>5567000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4397000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>4610000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3539000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>4315000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3714000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3188000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3076000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>3412000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1517000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2408000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2182000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2980000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2113000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>2494000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>2391000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>3542000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>3592000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3584000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3408000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3982000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3266000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>2597000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3047000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>1590000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>2085000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>2060000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>2031000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>2336000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>1361000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>2019000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>2267000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>2575000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>473000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>1688000</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1587000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1840000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>1509000</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>1518000</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8765,130 +8962,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1307000</v>
+      </c>
+      <c r="E83" s="3">
         <v>865000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1043000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1270000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1271000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>975000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>805000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>988000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>922000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>940000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>597000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>928000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>921000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>942000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1207000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>928000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>921000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>942000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>1237000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>1035000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1057000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>887000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>1406000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>853000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>686000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>824000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>656000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>654000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>675000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>658000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>469000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>468000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>517000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>390000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>413000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>451000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>455000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>434000</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>379000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>478000</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9009,8 +9210,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9131,8 +9335,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9253,8 +9460,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9375,8 +9585,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9497,130 +9710,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-2747000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-7098000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-2410000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-3332000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>11829000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-23976000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>11800000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-17323000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2525000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4360000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-17752000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>3747000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9666000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9865000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-13996000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-7553000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14913000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>239000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>349000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>2128000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>4615000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>26879000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>-25390000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-6867000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-16810000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>23836000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-136000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>13337000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>10531000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>17041000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-7179000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>14565000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-12729000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>12648000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1608000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>3357000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-9560000</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>90000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>-2482000</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-8443000</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9663,130 +9882,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-819000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-754000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-709000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-713000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-763000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-713000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-879000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-916000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-851000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-816000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-929000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-913000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-851000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-719000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-770000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-857000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-799000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-652000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-650000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-619000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-514000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-525000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-539000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-123000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-428000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-354000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-366000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-452000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-479000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-529000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-504000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-453000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-498000</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-410000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-452000</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-454000</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-373000</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-700000</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-670000</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-592000</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9907,8 +10130,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10029,130 +10255,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7204000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6600000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13397000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10676000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-17672000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-5034000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10150000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6696000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-13668000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1054000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8801000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>517000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>6241000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1041000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>898000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4161000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-8527000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>158000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15306000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-15147000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>3117000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-22561000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-460000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-3820000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-12510000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-21108000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-7840000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-7899000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-10595000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-7227000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-8815000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4763000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2381000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-6922000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-3563000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-11523000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>4863000</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-2168000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4520000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-2574000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10195,8 +10427,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10239,86 +10472,89 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R96" s="3">
         <v>-1255000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1267000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1200000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-1190000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-1210000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-1233000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-643000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-617000</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-612000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-560000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-491000</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-580000</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-397000</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-557000</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-579000</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-570000</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-587000</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-673000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-516000</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-599000</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-523000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-608000</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-443000</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-511000</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-435000</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-520000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10439,8 +10675,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10561,8 +10800,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10683,370 +10925,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>37060000</v>
+      </c>
+      <c r="E100" s="3">
         <v>36460000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>23970000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>9076000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21667000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>13045000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>15255000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>23048000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-404000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>8857000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>5694000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>361000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-2493000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6288000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>25975000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-4567000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-7985000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>9291000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>19715000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>11783000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>485000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>9564000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>34859000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2674000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3645000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>47954000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>9214000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-3919000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-1397000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-15864000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>10843000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>1536000</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>11463000</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>363000</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1272000</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>10168000</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>4643000</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>2722000</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>12835000</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-2895000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2567000</v>
+      </c>
+      <c r="E101" s="3">
         <v>1318000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-2603000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1895000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-598000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1198000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>1690000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1218000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-346000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>325000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3554000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3309000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3201000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-1327000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3554000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3309000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3201000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-1327000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-896000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1381000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>145000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1418000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1873000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1857000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>442000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1344000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1277000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1443000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>359000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-464000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-134000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-446000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2108000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>860000</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>264000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1837000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>692000</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>877000</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-2119000</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>340000</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>26606000</v>
+      </c>
+      <c r="E102" s="3">
         <v>21834000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7961000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5396000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>18391000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-14647000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>14302000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>924000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-12145000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>13073000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19169000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>3407000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6264000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-16869000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>16431000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19590000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-4800000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>8361000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3862000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2617000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>8362000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>12464000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>10882000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11504000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-25233000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>49338000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>2515000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>76000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1102000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6514000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-5285000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>10892000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-5755000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>6949000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1775000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>3532000</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-243000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>1521000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>3339000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-13581000</v>
       </c>
     </row>
